--- a/交易机会统计(已自动还原).xlsx
+++ b/交易机会统计(已自动还原).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EURUSD案例库\案例概览图\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EURUSD案例库\case-overview-images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0F9522-4FD8-4BFA-B456-9B539151E948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EA50F8-192E-4231-BEDD-DEA4DD49E8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="88">
   <si>
     <t>年限</t>
   </si>
@@ -262,6 +262,33 @@
   </si>
   <si>
     <t>EUR21</t>
+  </si>
+  <si>
+    <t>EUR22</t>
+  </si>
+  <si>
+    <t>下旗</t>
+  </si>
+  <si>
+    <t>释放途中的反转</t>
+  </si>
+  <si>
+    <t>EUR23</t>
+  </si>
+  <si>
+    <t>EUR24</t>
+  </si>
+  <si>
+    <t>EUR25</t>
+  </si>
+  <si>
+    <t>EUR26</t>
+  </si>
+  <si>
+    <t>EUR27</t>
+  </si>
+  <si>
+    <t>EUR28</t>
   </si>
 </sst>
 </file>
@@ -1855,118 +1882,396 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
+      <c r="A23" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N23" s="1">
+        <v>2</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
+      <c r="A24" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="1">
+        <v>2</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
+      <c r="A25" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
+      <c r="A26" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="1">
+        <v>3</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
+      <c r="A27" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="1">
+        <v>7</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" s="1">
+        <v>3</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
+      <c r="A28" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="1">
+        <v>4</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>2005</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="1">
+        <v>4</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N29" s="1">
+        <v>3</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
